--- a/data/Tonor/Feb/business_report.xlsx
+++ b/data/Tonor/Feb/business_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\buybox\data\Tonor\Feb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34868AE-D4AE-480A-AAE4-4F1AA64FD64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB580D8-3002-4B55-BA76-7140C96DF9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="111">
   <si>
     <t>(Parent) ASIN</t>
   </si>
@@ -141,12 +141,6 @@
     <t>TONOR Gaming Mic, USB Microphone for PC Computer, Cardioid Condenser Mic with Adjustable RGB Modes &amp; Brightness, Quick Mute, Gain Control, for Streaming, Podcasting, Recording, PS4/5 Desktop TC310</t>
   </si>
   <si>
-    <t>B0C8JDHLX9</t>
-  </si>
-  <si>
-    <t>TONOR T10 Microphone Boom Arm, Adjustable Microfono Stand Mic Arm with Extra-Large Pop Filter for HyperX Quadcast Blue Yeti Shure SM7B Rode Razer Seiren Mini SoloCast Elgato Wave, Recording Equipment</t>
-  </si>
-  <si>
     <t>B0CQX4K9P5</t>
   </si>
   <si>
@@ -177,18 +171,6 @@
     <t>TONOR Dynamic USB/Type-C Microphone for PC, RGB Podcast Computer Gaming Microphone with Arm Stand for Recording, Live, Streaming, YouTube, Vocals, Studio, Karaoke Microphone, Quick Mute Button, Black</t>
   </si>
   <si>
-    <t>B0BRKDLXCD</t>
-  </si>
-  <si>
-    <t>RGB Boom Arm, TONOR Adjustable Mic Stand with RGB Light for HyperX QuadCast/Blue Yeti/Shure SM7B/Rode NT1, Rotatable Suspension Boom Scissor Stand for Gaming Streaming Podcasting YouTube Recording T90</t>
-  </si>
-  <si>
-    <t>B089SJGQBH</t>
-  </si>
-  <si>
-    <t>TONOR XLR Condenser Microphone, Professional Cardioid Studio Mic Kit with T20 Boom Arm, Shock Mount, Pop Filter for Recording, Podcasting, Voice Over, Streaming, Home Studio, YouTube (TC20)</t>
-  </si>
-  <si>
     <t>B0CCV74CL7</t>
   </si>
   <si>
@@ -207,12 +189,6 @@
     <t>TONOR TM310 USB Conference Microphone for Laptop, Adjustable Computer PC Mic with Mute Button &amp; LED Indicator for Video Call Meeting, Mic for Desktop Zoom Skype YouTube, Plug-Play for MacOS Windows</t>
   </si>
   <si>
-    <t>B07TSN2H9D</t>
-  </si>
-  <si>
-    <t>TONOR Cardioid Condenser Microphone, USB Computer Mic Kit with 24mm Diaphragm/Spider Shock Mount for Podcasting, Gaming, Streaming, YouTube, Voice Over, Studio/Home Recording, TC-2030</t>
-  </si>
-  <si>
     <t>B089FVQD3Z</t>
   </si>
   <si>
@@ -231,12 +207,6 @@
     <t>TONOR TC777 Pro Gaming USB Microphone for PC, RGB Condenser Computer Mic with Tripod Stand, Quick Mute, Gain Control, for Gaming, Streaming, Podcasting, Recording, Cardioid Mic Kit for Laptop/PS4/PS5</t>
   </si>
   <si>
-    <t>B0CCVBQRFX</t>
-  </si>
-  <si>
-    <t>TONOR USB/XLR Microphone, Broadcast-Quality Dynamic Studio PC Mic with Boom Arm for Podcasting Recording Gaming Music Streaming Singing Voice-Over Noise Rejection, with 3.5mm Headphones Jack TD510+</t>
-  </si>
-  <si>
     <t>B08V1JS3NY</t>
   </si>
   <si>
@@ -309,12 +279,6 @@
     <t>TC310</t>
   </si>
   <si>
-    <t>FBA79115</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
     <t>FBA79697</t>
   </si>
   <si>
@@ -345,18 +309,6 @@
     <t>TD310+</t>
   </si>
   <si>
-    <t>FBA79112</t>
-  </si>
-  <si>
-    <t>T90</t>
-  </si>
-  <si>
-    <t>FBA77104</t>
-  </si>
-  <si>
-    <t>TC20</t>
-  </si>
-  <si>
     <t>FBA79114</t>
   </si>
   <si>
@@ -375,12 +327,6 @@
     <t>TM310</t>
   </si>
   <si>
-    <t>FBA77114</t>
-  </si>
-  <si>
-    <t>TC-2030</t>
-  </si>
-  <si>
     <t>FBA77105</t>
   </si>
   <si>
@@ -397,12 +343,6 @@
   </si>
   <si>
     <t>TC-777 PRO</t>
-  </si>
-  <si>
-    <t>FBA79582</t>
-  </si>
-  <si>
-    <t>TD510+</t>
   </si>
   <si>
     <t>FBA77115</t>
@@ -795,15 +735,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -871,49 +811,49 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2221</v>
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>341</v>
       </c>
       <c r="G2">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3">
-        <v>2.7000000000000001E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="I2" s="3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>3084</v>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J2">
+        <v>462</v>
       </c>
       <c r="K2">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="L2" s="3">
-        <v>2.8E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="M2" s="3">
-        <v>2.5999999999999999E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="N2" s="3">
-        <v>5.3600000000000002E-2</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="O2" s="3">
-        <v>6.0600000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -922,13 +862,13 @@
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="S2" s="3">
         <v>0</v>
       </c>
       <c r="T2" s="4">
-        <v>1863.5593220338983</v>
+        <v>1569.4915254237289</v>
       </c>
       <c r="U2" s="4">
         <v>0</v>
@@ -942,10 +882,10 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
@@ -957,34 +897,34 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2153</v>
+        <v>1639</v>
       </c>
       <c r="G3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3">
-        <v>2.5999999999999999E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="I3" s="3">
-        <v>3.3E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="J3" s="2">
-        <v>2965</v>
+        <v>2300</v>
       </c>
       <c r="K3">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L3" s="3">
-        <v>2.7000000000000001E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="M3" s="3">
-        <v>2.8999999999999998E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="N3" s="3">
-        <v>3.5700000000000003E-2</v>
+        <v>5.6899999999999999E-2</v>
       </c>
       <c r="O3" s="3">
-        <v>0</v>
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -993,13 +933,13 @@
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="S3" s="3">
         <v>0</v>
       </c>
       <c r="T3" s="4">
-        <v>1948.3050847457628</v>
+        <v>1905.9322033898306</v>
       </c>
       <c r="U3" s="4">
         <v>0</v>
@@ -1013,70 +953,70 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2">
-        <v>1080</v>
+        <v>1675</v>
       </c>
       <c r="G4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" s="3">
-        <v>1.2999999999999999E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I4" s="3">
-        <v>1.5E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="J4" s="2">
-        <v>1574</v>
+        <v>2319</v>
       </c>
       <c r="K4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L4" s="3">
-        <v>1.4E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="M4" s="3">
-        <v>1.1000000000000001E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="N4" s="3">
-        <v>0.1021</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3">
-        <v>5.2600000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3">
         <v>0</v>
       </c>
       <c r="T4" s="4">
-        <v>3304.2372881355932</v>
+        <v>0</v>
       </c>
       <c r="U4" s="4">
         <v>0</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -1084,46 +1024,46 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2">
-        <v>4815</v>
+        <v>1401</v>
       </c>
       <c r="G5">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3">
-        <v>5.8999999999999999E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="I5" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="J5" s="2">
-        <v>7181</v>
+        <v>2154</v>
       </c>
       <c r="K5">
-        <v>188</v>
+        <v>51</v>
       </c>
       <c r="L5" s="3">
-        <v>6.4999999999999997E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="M5" s="3">
-        <v>8.6E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="N5" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1155,354 +1095,354 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>685</v>
+        <v>28</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3616</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3">
-        <v>5.9999999999999995E-4</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="I6" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="J6">
-        <v>909</v>
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>5222</v>
       </c>
       <c r="K6">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="L6" s="3">
-        <v>5.9999999999999995E-4</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="M6" s="3">
-        <v>1E-3</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="N6" s="3">
-        <v>0.98319999999999996</v>
+        <v>0.25929999999999997</v>
       </c>
       <c r="O6" s="3">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
       <c r="P6">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" s="3">
-        <v>2.7699999999999999E-2</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="S6" s="3">
-        <v>0.1</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T6" s="4">
-        <v>32358.474576271186</v>
+        <v>67378.813559322036</v>
       </c>
       <c r="U6" s="4">
-        <v>4398</v>
+        <v>1849</v>
       </c>
       <c r="V6">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>729</v>
+        <v>645</v>
       </c>
       <c r="G7">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H7" s="3">
-        <v>6.9999999999999999E-4</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="I7" s="3">
-        <v>3.3999999999999998E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="J7">
-        <v>982</v>
+        <v>951</v>
       </c>
       <c r="K7">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L7" s="3">
-        <v>6.9999999999999999E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="M7" s="3">
-        <v>3.0999999999999999E-3</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="N7" s="3">
-        <v>0.67830000000000001</v>
+        <v>0.91620000000000001</v>
       </c>
       <c r="O7" s="3">
-        <v>0.43330000000000002</v>
+        <v>0.81159999999999999</v>
       </c>
       <c r="P7">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R7" s="3">
-        <v>2.3300000000000001E-2</v>
+        <v>3.8800000000000001E-2</v>
       </c>
       <c r="S7" s="3">
-        <v>2.9899999999999999E-2</v>
+        <v>0.20749999999999999</v>
       </c>
       <c r="T7" s="4">
-        <v>43366.305084745763</v>
+        <v>54810.169491525427</v>
       </c>
       <c r="U7" s="4">
-        <v>5998</v>
+        <v>29589</v>
       </c>
       <c r="V7">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2">
-        <v>6797</v>
+        <v>2259</v>
       </c>
       <c r="G8">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="H8" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="I8" s="3">
-        <v>8.3000000000000001E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="J8" s="2">
-        <v>10031</v>
+        <v>3605</v>
       </c>
       <c r="K8">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="L8" s="3">
-        <v>7.1000000000000004E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="M8" s="3">
-        <v>9.1000000000000004E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="N8" s="3">
-        <v>4.2000000000000003E-2</v>
+        <v>0.33279999999999998</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>0.45240000000000002</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="3">
-        <v>1.5E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="T8" s="4">
-        <v>15069.491525423729</v>
+        <v>30577.118644067799</v>
       </c>
       <c r="U8" s="4">
-        <v>0</v>
+        <v>1899</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2">
-        <v>5298</v>
+        <v>32</v>
+      </c>
+      <c r="F9">
+        <v>509</v>
       </c>
       <c r="G9">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="H9" s="3">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="I9" s="3">
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>8195</v>
+        <v>6.3E-3</v>
+      </c>
+      <c r="J9">
+        <v>725</v>
       </c>
       <c r="K9">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="L9" s="3">
-        <v>5.7999999999999996E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="M9" s="3">
-        <v>5.8999999999999999E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="N9" s="3">
-        <v>5.6899999999999999E-2</v>
+        <v>0.57830000000000004</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>0.36840000000000001</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R9" s="3">
-        <v>1.9E-3</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>0.1148</v>
       </c>
       <c r="T9" s="4">
-        <v>19166.050847457627</v>
+        <v>33039.830508474581</v>
       </c>
       <c r="U9" s="4">
-        <v>0</v>
+        <v>20993</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10">
-        <v>148</v>
+        <v>34</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2350</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="H10" s="3">
-        <v>1E-4</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="I10" s="3">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="J10">
-        <v>200</v>
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>3419</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="L10" s="3">
-        <v>1E-4</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="M10" s="3">
-        <v>2.9999999999999997E-4</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="N10" s="3">
-        <v>0.96150000000000002</v>
+        <v>0.1827</v>
       </c>
       <c r="O10" s="3">
-        <v>0.875</v>
+        <v>0.2</v>
       </c>
       <c r="P10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>6.08E-2</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
       <c r="T10" s="4">
-        <v>13000.84745762712</v>
+        <v>16942.372881355932</v>
       </c>
       <c r="U10" s="4">
         <v>0</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -1510,70 +1450,70 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1586</v>
+        <v>44</v>
+      </c>
+      <c r="F11">
+        <v>364</v>
       </c>
       <c r="G11">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H11" s="3">
-        <v>1.5E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="I11" s="3">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>2858</v>
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="J11">
+        <v>701</v>
       </c>
       <c r="K11">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="L11" s="3">
-        <v>2E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="M11" s="3">
-        <v>2.0999999999999999E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="N11" s="3">
-        <v>9.5500000000000002E-2</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="O11" s="3">
-        <v>0.13789999999999999</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11" s="3">
-        <v>4.4000000000000003E-3</v>
+        <v>1.37E-2</v>
       </c>
       <c r="S11" s="3">
         <v>0</v>
       </c>
       <c r="T11" s="4">
-        <v>9612.7118644067796</v>
+        <v>8216.1016949152545</v>
       </c>
       <c r="U11" s="4">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -1581,141 +1521,141 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1063</v>
+        <v>52</v>
+      </c>
+      <c r="F12">
+        <v>139</v>
       </c>
       <c r="G12">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="H12" s="3">
-        <v>1E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="I12" s="3">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1531</v>
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="J12">
+        <v>185</v>
       </c>
       <c r="K12">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="L12" s="3">
-        <v>1.1000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="M12" s="3">
-        <v>5.1000000000000004E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="N12" s="3">
-        <v>0.27760000000000001</v>
+        <v>0.49130000000000001</v>
       </c>
       <c r="O12" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" s="3">
-        <v>8.5000000000000006E-3</v>
+        <v>2.1600000000000001E-2</v>
       </c>
       <c r="S12" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="T12" s="4">
-        <v>19029.661016949154</v>
+        <v>7443.2203389830511</v>
       </c>
       <c r="U12" s="4">
-        <v>9780</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13">
-        <v>543</v>
+        <v>24</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1639</v>
       </c>
       <c r="G13">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H13" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>3.3E-3</v>
       </c>
       <c r="I13" s="3">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="J13">
-        <v>742</v>
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2300</v>
       </c>
       <c r="K13">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="L13" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="M13" s="3">
-        <v>1E-3</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="N13" s="3">
-        <v>7.7299999999999994E-2</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="O13" s="3">
-        <v>0</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="P13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13" s="3">
-        <v>1.0999999999999999E-2</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="S13" s="3">
         <v>0</v>
       </c>
       <c r="T13" s="4">
-        <v>12205.508474576272</v>
+        <v>7623.7288135593226</v>
       </c>
       <c r="U13" s="4">
         <v>0</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -1723,70 +1663,70 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F14">
-        <v>984</v>
+        <v>101</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="I14" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1433</v>
+        <v>1E-4</v>
+      </c>
+      <c r="J14">
+        <v>144</v>
       </c>
       <c r="K14">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3">
-        <v>1E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="M14" s="3">
-        <v>1.1000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="N14" s="3">
-        <v>3.85E-2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <v>5.1000000000000004E-3</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="4">
-        <v>8806.3898305084749</v>
+        <v>5591.5254237288136</v>
       </c>
       <c r="U14" s="4">
         <v>0</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -1794,70 +1734,70 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F15" s="2">
-        <v>1381</v>
+        <v>1401</v>
       </c>
       <c r="G15">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H15" s="3">
-        <v>1.2999999999999999E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I15" s="3">
-        <v>1.1999999999999999E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="J15" s="2">
-        <v>2428</v>
+        <v>2154</v>
       </c>
       <c r="K15">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="L15" s="3">
-        <v>1.6999999999999999E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="M15" s="3">
-        <v>1.1999999999999999E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="N15" s="3">
-        <v>0.12239999999999999</v>
+        <v>0.1095</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <v>3.5999999999999999E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
       <c r="T15" s="4">
-        <v>7878.7627118644077</v>
+        <v>10166.949152542373</v>
       </c>
       <c r="U15" s="4">
         <v>0</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -1865,70 +1805,70 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F16">
-        <v>486</v>
+        <v>582</v>
       </c>
       <c r="G16">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H16" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="I16" s="3">
-        <v>5.9999999999999995E-4</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="J16">
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="K16">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L16" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="M16" s="3">
-        <v>5.9999999999999995E-4</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="N16" s="3">
-        <v>0.98839999999999995</v>
+        <v>0.17480000000000001</v>
       </c>
       <c r="O16" s="3">
-        <v>1</v>
+        <v>5.2600000000000001E-2</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <v>8.2000000000000007E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="S16" s="3">
         <v>0</v>
       </c>
       <c r="T16" s="4">
-        <v>13147.457627118645</v>
+        <v>4235.593220338983</v>
       </c>
       <c r="U16" s="4">
         <v>0</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W16">
         <v>0</v>
@@ -1936,70 +1876,70 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17">
+        <v>634</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J17">
+        <v>900</v>
+      </c>
+      <c r="K17">
         <v>22</v>
       </c>
-      <c r="F17" s="2">
-        <v>1784</v>
-      </c>
-      <c r="G17">
-        <v>40</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="M17" s="3">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="I17" s="3">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="J17" s="2">
-        <v>2500</v>
-      </c>
-      <c r="K17">
-        <v>49</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1.8E-3</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1.8E-3</v>
-      </c>
       <c r="N17" s="3">
-        <v>9.6600000000000005E-2</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="O17" s="3">
-        <v>6.4500000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17">
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <v>1.1000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
       <c r="T17" s="4">
-        <v>3727.1186440677966</v>
+        <v>2202.5423728813562</v>
       </c>
       <c r="U17" s="4">
         <v>0</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W17">
         <v>0</v>
@@ -2007,70 +1947,70 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1675</v>
+      </c>
+      <c r="G18">
+        <v>34</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2319</v>
+      </c>
+      <c r="K18">
         <v>50</v>
       </c>
-      <c r="F18">
-        <v>82</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="J18">
-        <v>137</v>
-      </c>
-      <c r="K18">
-        <v>5</v>
-      </c>
       <c r="L18" s="3">
-        <v>1E-4</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="M18" s="3">
-        <v>2.0000000000000001E-4</v>
+        <v>3.8E-3</v>
       </c>
       <c r="N18" s="3">
-        <v>0.90600000000000003</v>
+        <v>7.8899999999999998E-2</v>
       </c>
       <c r="O18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>2.4400000000000002E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
       <c r="T18" s="4">
-        <v>8472.8813559322043</v>
+        <v>1778.8135593220341</v>
       </c>
       <c r="U18" s="4">
         <v>0</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -2078,70 +2018,70 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="2">
-        <v>2153</v>
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>542</v>
       </c>
       <c r="G19">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3">
-        <v>2E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="I19" s="3">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="J19" s="2">
-        <v>2965</v>
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="J19">
+        <v>739</v>
       </c>
       <c r="K19">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="L19" s="3">
-        <v>2.0999999999999999E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="M19" s="3">
-        <v>2.3E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="N19" s="3">
-        <v>9.8799999999999999E-2</v>
+        <v>0.12479999999999999</v>
       </c>
       <c r="O19" s="3">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19">
         <v>0</v>
       </c>
       <c r="R19" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="S19" s="3">
         <v>0</v>
       </c>
       <c r="T19" s="4">
-        <v>3794.9152542372885</v>
+        <v>2033.0508474576272</v>
       </c>
       <c r="U19" s="4">
         <v>0</v>
       </c>
       <c r="V19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -2155,64 +2095,64 @@
         <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="2">
-        <v>2289</v>
+        <v>62</v>
+      </c>
+      <c r="F20">
+        <v>55</v>
       </c>
       <c r="G20">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>2.2000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="I20" s="3">
-        <v>1.4E-3</v>
-      </c>
-      <c r="J20" s="2">
-        <v>3022</v>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>82</v>
       </c>
       <c r="K20">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>2.0999999999999999E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="M20" s="3">
-        <v>1.4E-3</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>4.9700000000000001E-2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="4">
-        <v>5109.7796610169498</v>
+        <v>2880.5084745762715</v>
       </c>
       <c r="U20" s="4">
         <v>0</v>
       </c>
       <c r="V20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -2220,70 +2160,70 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21">
-        <v>14</v>
+        <v>46</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2326</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>21</v>
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2982</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>2E-3</v>
       </c>
       <c r="N21" s="3">
-        <v>1</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>7.1400000000000005E-2</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21">
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>0.1429</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="S21" s="3">
         <v>0</v>
       </c>
       <c r="T21" s="4">
-        <v>4405.0847457627124</v>
+        <v>2788.1355932203392</v>
       </c>
       <c r="U21" s="4">
         <v>0</v>
       </c>
       <c r="V21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -2291,141 +2231,141 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F22">
-        <v>832</v>
+        <v>84</v>
       </c>
       <c r="G22">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>8.0000000000000004E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="I22" s="3">
-        <v>2.3E-3</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1064</v>
+        <v>1E-4</v>
+      </c>
+      <c r="J22">
+        <v>101</v>
       </c>
       <c r="K22">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="L22" s="3">
-        <v>6.9999999999999999E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="M22" s="3">
-        <v>2E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="N22" s="3">
-        <v>0.3543</v>
+        <v>7.0699999999999999E-2</v>
       </c>
       <c r="O22" s="3">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>2.3999999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>2.2700000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="T22" s="4">
-        <v>5145.7118644067796</v>
+        <v>0</v>
       </c>
       <c r="U22" s="4">
-        <v>3072.94</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F23">
-        <v>711</v>
+        <v>200</v>
       </c>
       <c r="G23">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" s="3">
-        <v>6.9999999999999999E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="I23" s="3">
-        <v>6.9999999999999999E-4</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="J23">
-        <v>973</v>
+        <v>266</v>
       </c>
       <c r="K23">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L23" s="3">
-        <v>6.9999999999999999E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="M23" s="3">
-        <v>8.0000000000000004E-4</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="N23" s="3">
-        <v>0.34110000000000001</v>
+        <v>0.1888</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>1.4E-3</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
       <c r="T23" s="4">
-        <v>3388.9830508474579</v>
+        <v>0</v>
       </c>
       <c r="U23" s="4">
         <v>0</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -2433,70 +2373,70 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F24">
-        <v>358</v>
+        <v>110</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H24" s="3">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="I24" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="J24">
-        <v>488</v>
+        <v>132</v>
       </c>
       <c r="K24">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="L24" s="3">
-        <v>2.9999999999999997E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="M24" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="N24" s="3">
-        <v>0.2329</v>
+        <v>0.1694</v>
       </c>
       <c r="O24" s="3">
-        <v>0.26669999999999999</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>2.8E-3</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="4">
-        <v>2456.7796610169494</v>
+        <v>0</v>
       </c>
       <c r="U24" s="4">
         <v>0</v>
       </c>
       <c r="V24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -2504,70 +2444,70 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F25">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="M25" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="N25" s="3">
-        <v>0.307</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
       </c>
       <c r="R25" s="3">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3">
         <v>0</v>
       </c>
       <c r="T25" s="4">
-        <v>2016.1016949152543</v>
+        <v>0</v>
       </c>
       <c r="U25" s="4">
         <v>0</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -2575,70 +2515,70 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1080</v>
+        <v>48</v>
+      </c>
+      <c r="F26">
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1574</v>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>24</v>
       </c>
       <c r="K26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>1.1000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>8.4199999999999997E-2</v>
+        <v>1</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>8.9999999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
       <c r="T26" s="4">
-        <v>3412.6610169491528</v>
+        <v>0</v>
       </c>
       <c r="U26" s="4">
         <v>0</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -2646,427 +2586,72 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="2">
-        <v>1946</v>
+        <v>36</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>1.8E-3</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="J27" s="2">
-        <v>2894</v>
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>2.3E-3</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>6.4699999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>5.8799999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
       <c r="T27" s="4">
-        <v>1694.0677966101696</v>
+        <v>0</v>
       </c>
       <c r="U27" s="4">
         <v>0</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28">
-        <v>102</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>147</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
-        <v>1</v>
-      </c>
-      <c r="O28" s="3">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28" s="3">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="S28" s="3">
-        <v>0</v>
-      </c>
-      <c r="T28" s="4">
-        <v>5338.1355932203396</v>
-      </c>
-      <c r="U28" s="4">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>1</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>99</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>1</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="4">
-        <v>0</v>
-      </c>
-      <c r="U29" s="4">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30">
-        <v>312</v>
-      </c>
-      <c r="G30">
-        <v>7</v>
-      </c>
-      <c r="H30" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="I30" s="3">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="J30">
-        <v>356</v>
-      </c>
-      <c r="K30">
-        <v>9</v>
-      </c>
-      <c r="L30" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="M30" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="N30" s="3">
-        <v>0.31659999999999999</v>
-      </c>
-      <c r="O30" s="3">
-        <v>0.28570000000000001</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30" s="3">
-        <v>0</v>
-      </c>
-      <c r="S30" s="3">
-        <v>0</v>
-      </c>
-      <c r="T30" s="4">
-        <v>0</v>
-      </c>
-      <c r="U30" s="4">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>81</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
-        <v>1</v>
-      </c>
-      <c r="O31" s="3">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3">
-        <v>0</v>
-      </c>
-      <c r="S31" s="3">
-        <v>0</v>
-      </c>
-      <c r="T31" s="4">
-        <v>0</v>
-      </c>
-      <c r="U31" s="4">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32">
-        <v>225</v>
-      </c>
-      <c r="G32">
-        <v>8</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="J32">
-        <v>306</v>
-      </c>
-      <c r="K32">
-        <v>11</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="M32" s="3">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0.19339999999999999</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="4">
-        <v>0</v>
-      </c>
-      <c r="U32" s="4">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
         <v>0</v>
       </c>
     </row>
